--- a/Paradigms/P0200_GoalDirectedMovement.xlsx
+++ b/Paradigms/P0200_GoalDirectedMovement.xlsx
@@ -1330,7 +1330,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1342,6 +1342,12 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
@@ -1451,7 +1457,7 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
@@ -1476,7 +1482,7 @@
       <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+      <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -53869,7 +53875,7 @@
     <col min="9" max="9" style="18" width="13.005" customWidth="1" bestFit="1"/>
     <col min="10" max="10" style="20" width="13.005" customWidth="1" bestFit="1"/>
     <col min="11" max="11" style="20" width="13.005" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="21" width="22.290714285714284" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="18" width="22.290714285714284" customWidth="1" bestFit="1"/>
     <col min="13" max="13" style="21" width="13.005" customWidth="1" bestFit="1"/>
     <col min="14" max="14" style="20" width="13.005" customWidth="1" bestFit="1"/>
     <col min="15" max="15" style="20" width="13.005" customWidth="1" bestFit="1"/>
@@ -53878,7 +53884,7 @@
     <col min="18" max="18" style="20" width="13.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -53924,18 +53930,18 @@
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="8">
         <v>1</v>
       </c>
       <c r="B2" s="8">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C2" s="8">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="D2" s="8">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>11</v>
@@ -53950,17 +53956,17 @@
         <v>0</v>
       </c>
       <c r="I2" s="8">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J2" s="3"/>
       <c r="K2" s="4" t="s">
         <v>12</v>
       </c>
       <c r="L2" s="9">
-        <v>160</v>
+        <v>210</v>
       </c>
       <c r="M2" s="9">
-        <v>160</v>
+        <v>210</v>
       </c>
       <c r="N2" s="10"/>
       <c r="O2" s="3"/>
@@ -53968,13 +53974,13 @@
         <v>13</v>
       </c>
       <c r="Q2" s="11">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="R2" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -53998,13 +54004,13 @@
         <v>16</v>
       </c>
       <c r="Q3" s="11">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="R3" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="8">
         <v>2</v>
       </c>
@@ -54046,13 +54052,13 @@
         <v>20</v>
       </c>
       <c r="Q4" s="11">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="R4" s="6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="8">
         <v>3</v>
       </c>
@@ -54090,13 +54096,13 @@
         <v>23</v>
       </c>
       <c r="Q5" s="11">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="R5" s="6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="8">
         <v>4</v>
       </c>
@@ -54140,7 +54146,7 @@
       <c r="Q6" s="7"/>
       <c r="R6" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="8">
         <v>5</v>
       </c>
@@ -54182,7 +54188,7 @@
       <c r="Q7" s="7"/>
       <c r="R7" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -54206,7 +54212,7 @@
       <c r="Q8" s="12"/>
       <c r="R8" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -54230,7 +54236,7 @@
       <c r="Q9" s="12"/>
       <c r="R9" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -54252,7 +54258,7 @@
       <c r="Q10" s="12"/>
       <c r="R10" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="12"/>
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
@@ -54272,7 +54278,7 @@
       <c r="Q11" s="12"/>
       <c r="R11" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="12"/>
       <c r="B12" s="12"/>
       <c r="C12" s="12"/>
@@ -54292,7 +54298,7 @@
       <c r="Q12" s="12"/>
       <c r="R12" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="12"/>
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
@@ -54312,7 +54318,7 @@
       <c r="Q13" s="12"/>
       <c r="R13" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="12"/>
       <c r="B14" s="12"/>
       <c r="C14" s="12"/>
@@ -54332,7 +54338,7 @@
       <c r="Q14" s="12"/>
       <c r="R14" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
